--- a/figures/supplementary/Raw-p-val.xlsx
+++ b/figures/supplementary/Raw-p-val.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\goel107\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF45B8CB-3D95-41FF-8E9D-0AA4818DC83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BD2D14-B80E-409D-8220-02EC9F17C7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{175B077B-3F30-42EC-9AF7-64FB422E807F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{175B077B-3F30-42EC-9AF7-64FB422E807F}"/>
   </bookViews>
   <sheets>
     <sheet name="degree_centrality" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="54">
   <si>
     <t>Figure</t>
   </si>
@@ -581,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE2F8EE5-9576-4048-AC83-055C6C18433B}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -764,40 +764,46 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1">
-        <v>9.6709999999999994E-6</v>
+        <v>2.926E-14</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1">
+        <v>9.6709999999999994E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.764E-6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2">
         <v>0.107</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="2">
-        <v>4.5399999999999998E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2">
-        <v>4.1399999999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -805,149 +811,165 @@
         <v>9</v>
       </c>
       <c r="C22" s="2">
+        <v>4.5399999999999998E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2">
+        <v>4.1399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2">
         <v>2.7500000000000002E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0.98250000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0.99170000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="2">
-        <v>0.85029999999999994</v>
+        <v>0.98250000000000004</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="2">
-        <v>2.098E-4</v>
+        <v>0.99170000000000003</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="2">
-        <v>0.98450000000000004</v>
+        <v>0.85029999999999994</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="2">
-        <v>0.99719999999999998</v>
+        <v>2.098E-4</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="2">
-        <v>0.96430000000000005</v>
+        <v>0.98450000000000004</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="2">
-        <v>0.51549999999999996</v>
+        <v>0.99719999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="2">
-        <v>0.7</v>
+        <v>0.96430000000000005</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="2">
-        <v>0.27</v>
+        <v>0.51549999999999996</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="2">
-        <v>0.37</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="2">
-        <v>3.7999999999999999E-2</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>48</v>
       </c>
-      <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="2">
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="2">
         <v>0.96</v>
       </c>
     </row>

--- a/figures/supplementary/Raw-p-val.xlsx
+++ b/figures/supplementary/Raw-p-val.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\goel107\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BD2D14-B80E-409D-8220-02EC9F17C7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF486E2D-BB69-41B9-84BF-1B555801671F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{175B077B-3F30-42EC-9AF7-64FB422E807F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{175B077B-3F30-42EC-9AF7-64FB422E807F}"/>
   </bookViews>
   <sheets>
     <sheet name="degree_centrality" sheetId="1" r:id="rId1"/>
-    <sheet name="betweenness_centrality" sheetId="2" r:id="rId2"/>
+    <sheet name="degree_centrality2" sheetId="3" r:id="rId2"/>
+    <sheet name="betweenness_centrality" sheetId="2" r:id="rId3"/>
+    <sheet name="betweenness_centrality2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="68">
   <si>
     <t>Figure</t>
   </si>
@@ -199,6 +201,48 @@
   </si>
   <si>
     <t>S5J</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>AE-MS</t>
+  </si>
+  <si>
+    <t>Y2H</t>
+  </si>
+  <si>
+    <t>Molecular abundance</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Protein half-life</t>
+  </si>
+  <si>
+    <t>Odds of essentiality</t>
+  </si>
+  <si>
+    <t>Rosetta</t>
+  </si>
+  <si>
+    <t>Ghosh&amp;Dill</t>
+  </si>
+  <si>
+    <t>Cagiada</t>
+  </si>
+  <si>
+    <t>Meltome Atlas</t>
+  </si>
+  <si>
+    <t>Hubs&amp;Non-hubs</t>
+  </si>
+  <si>
+    <t>Static&amp;Dynamic hubs</t>
   </si>
 </sst>
 </file>
@@ -581,395 +625,561 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE2F8EE5-9576-4048-AC83-055C6C18433B}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
         <v>1.7719999999999999E-66</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:7">
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2">
         <v>0.33789999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1">
         <v>8.5859999999999999E-38</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:7">
       <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2">
         <v>0.99760000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1.784E-13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1">
+        <v>7.2980000000000005E-16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
       <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2.8869999999999998E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2.9950000000000001E-14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1">
-        <v>7.2980000000000005E-16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3.996E-17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2.9950000000000001E-14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3.531E-28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3.996E-17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3.531E-28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2.2000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1.1059999999999999E-8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2.2000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1">
+        <v>9.6709999999999994E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1.1059999999999999E-8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1">
-        <v>2.926E-14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2">
+        <v>4.5399999999999998E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="1">
-        <v>9.6709999999999994E-6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2">
+        <v>4.1399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="B20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1.764E-6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2.7500000000000002E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2">
-        <v>0.107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.98250000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
       <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="2">
-        <v>4.5399999999999998E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.99170000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
       <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="2">
-        <v>4.1399999999999999E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.85029999999999994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
       <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2.7500000000000002E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2.098E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0.98250000000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.98450000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="2">
-        <v>0.99170000000000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.99719999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0.85029999999999994</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.96430000000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="2">
-        <v>2.098E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.51549999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0.98450000000000004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0.99719999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="2">
-        <v>0.96430000000000005</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="2">
-        <v>0.51549999999999996</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="C32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="2">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="2">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="2">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="2">
-        <v>3.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="2">
+        <v>57</v>
+      </c>
+      <c r="C33" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="2">
         <v>0.96</v>
       </c>
     </row>
@@ -979,274 +1189,558 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB4C916-DCBC-4B2E-B78D-6D8CFE40C854}">
-  <dimension ref="A1:C25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B507DD-DC21-49C5-A1E4-E1DAC6224A2A}">
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.784E-13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.8869999999999998E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2.926E-14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.764E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB4C916-DCBC-4B2E-B78D-6D8CFE40C854}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
       <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
         <v>8.407E-32</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:7">
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2">
         <v>0.69059999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2">
         <v>5.6910000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:7">
       <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2">
         <v>0.99009999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.99370000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.99719999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.99960000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.98009999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.58299999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.84560000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.36470000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.55530000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C212671C-0208-4297-9BF9-E241697E56B7}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1">
+      <c r="E2" s="1">
         <v>8.3249999999999994E-8</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="B7" t="s">
+    <row r="3" spans="1:5">
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2">
+      <c r="E3" s="2">
         <v>2.0579999999999999E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.99370000000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.99719999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.99960000000000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.98009999999999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.58299999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.84560000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0.36470000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0.55530000000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="2">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0.7</v>
       </c>
     </row>
   </sheetData>
